--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747725</v>
+        <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>82549</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639454</v>
+        <v>639460</v>
       </c>
       <c r="R2" t="n">
-        <v>7096322</v>
+        <v>7096324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R4" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747726</v>
+        <v>122747728</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639460</v>
+        <v>639499</v>
       </c>
       <c r="R2" t="n">
-        <v>7096324</v>
+        <v>7096307</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747727</v>
+        <v>122747726</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639461</v>
+        <v>639460</v>
       </c>
       <c r="R3" t="n">
         <v>7096324</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747728</v>
+        <v>122747727</v>
       </c>
       <c r="B5" t="n">
         <v>74863</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639499</v>
+        <v>639461</v>
       </c>
       <c r="R5" t="n">
-        <v>7096307</v>
+        <v>7096324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747728</v>
+        <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639499</v>
+        <v>639460</v>
       </c>
       <c r="R2" t="n">
-        <v>7096307</v>
+        <v>7096324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R3" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747725</v>
+        <v>122747727</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639454</v>
+        <v>639461</v>
       </c>
       <c r="R4" t="n">
-        <v>7096322</v>
+        <v>7096324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747727</v>
+        <v>122747728</v>
       </c>
       <c r="B5" t="n">
         <v>74863</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639461</v>
+        <v>639499</v>
       </c>
       <c r="R5" t="n">
-        <v>7096324</v>
+        <v>7096307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R2" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747725</v>
+        <v>122747727</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639454</v>
+        <v>639461</v>
       </c>
       <c r="R3" t="n">
-        <v>7096322</v>
+        <v>7096324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747727</v>
+        <v>122747726</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639461</v>
+        <v>639460</v>
       </c>
       <c r="R4" t="n">
         <v>7096324</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747725</v>
+        <v>122747727</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639454</v>
+        <v>639461</v>
       </c>
       <c r="R2" t="n">
-        <v>7096322</v>
+        <v>7096324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747727</v>
+        <v>122747726</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639461</v>
+        <v>639460</v>
       </c>
       <c r="R3" t="n">
         <v>7096324</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R4" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747727</v>
+        <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639461</v>
+        <v>639460</v>
       </c>
       <c r="R2" t="n">
         <v>7096324</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R3" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747725</v>
+        <v>122747728</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639454</v>
+        <v>639499</v>
       </c>
       <c r="R4" t="n">
-        <v>7096322</v>
+        <v>7096307</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747728</v>
+        <v>122747727</v>
       </c>
       <c r="B5" t="n">
         <v>74863</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639499</v>
+        <v>639461</v>
       </c>
       <c r="R5" t="n">
-        <v>7096307</v>
+        <v>7096324</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>82553</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R2" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747725</v>
+        <v>122747726</v>
       </c>
       <c r="B3" t="n">
-        <v>82553</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639454</v>
+        <v>639460</v>
       </c>
       <c r="R3" t="n">
-        <v>7096322</v>
+        <v>7096324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747726</v>
+        <v>122747728</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639460</v>
+        <v>639499</v>
       </c>
       <c r="R3" t="n">
-        <v>7096324</v>
+        <v>7096307</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747728</v>
+        <v>122747726</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639499</v>
+        <v>639460</v>
       </c>
       <c r="R4" t="n">
-        <v>7096307</v>
+        <v>7096324</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747725</v>
+        <v>122747727</v>
       </c>
       <c r="B2" t="n">
-        <v>82553</v>
+        <v>74866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639454</v>
+        <v>639461</v>
       </c>
       <c r="R2" t="n">
-        <v>7096322</v>
+        <v>7096324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122747728</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>82556</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R4" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747727</v>
+        <v>122747726</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>90973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639461</v>
+        <v>639460</v>
       </c>
       <c r="R5" t="n">
         <v>7096324</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747727</v>
+        <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>74866</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639461</v>
+        <v>639460</v>
       </c>
       <c r="R2" t="n">
         <v>7096324</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747728</v>
+        <v>122747727</v>
       </c>
       <c r="B3" t="n">
         <v>74866</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639499</v>
+        <v>639461</v>
       </c>
       <c r="R3" t="n">
-        <v>7096307</v>
+        <v>7096324</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747726</v>
+        <v>122747728</v>
       </c>
       <c r="B5" t="n">
-        <v>90973</v>
+        <v>74866</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639460</v>
+        <v>639499</v>
       </c>
       <c r="R5" t="n">
-        <v>7096324</v>
+        <v>7096307</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>122747727</v>
       </c>
       <c r="B3" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>83161</v>
+        <v>83163</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>122747728</v>
       </c>
       <c r="B5" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>122747727</v>
       </c>
       <c r="B3" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>83163</v>
+        <v>83165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>122747728</v>
       </c>
       <c r="B5" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>122747727</v>
       </c>
       <c r="B3" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>122747725</v>
       </c>
       <c r="B4" t="n">
-        <v>83165</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>122747728</v>
       </c>
       <c r="B5" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747726</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747726</v>
+        <v>122747725</v>
       </c>
       <c r="B2" t="n">
-        <v>91937</v>
+        <v>83222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639460</v>
+        <v>639454</v>
       </c>
       <c r="R2" t="n">
-        <v>7096324</v>
+        <v>7096322</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +779,7 @@
         <v>122747727</v>
       </c>
       <c r="B3" t="n">
-        <v>83314</v>
+        <v>83358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747725</v>
+        <v>122747728</v>
       </c>
       <c r="B4" t="n">
-        <v>83180</v>
+        <v>83358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639454</v>
+        <v>639499</v>
       </c>
       <c r="R4" t="n">
-        <v>7096322</v>
+        <v>7096307</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,107 +971,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>122747728</v>
-      </c>
-      <c r="B5" t="n">
-        <v>83314</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Renskinns- NV, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>639499</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7096307</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Jessica  Åström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 53238-2024 artfynd.xlsx
+++ b/artfynd/A 53238-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747727</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>